--- a/data/tags/אלבומים חדשים/sites/rotter/2026-06-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-06-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרויקט אסי עזר - כל מה שעוזר</v>
+        <v>נינט טייב - אני נינה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24473&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24474&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:49</v>
+        <v>09:26</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרויקט אסי עזר - כל מה שעוזר</v>
+        <v>נינט טייב - אני נינה</v>
       </c>
     </row>
   </sheetData>
